--- a/excel/1000(n)/Random_Dataset.xlsx
+++ b/excel/1000(n)/Random_Dataset.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="28">
   <si>
     <t xml:space="preserve">Algorithm </t>
   </si>
@@ -222,67 +222,67 @@
         <v>1000.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>2826700.0</v>
+        <v>1047900.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1128600.0</v>
+        <v>1193000.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>996100.0</v>
+        <v>1061600.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1161900.0</v>
+        <v>850300.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>1095500.0</v>
+        <v>1127100.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>1151900.0</v>
+        <v>571200.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>735400.0</v>
+        <v>1171200.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>904200.0</v>
+        <v>589600.0</v>
       </c>
       <c r="K2" t="n" s="0">
+        <v>770700.0</v>
+      </c>
+      <c r="L2" t="n" s="0">
+        <v>1141400.0</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>566600.0</v>
+      </c>
+      <c r="N2" t="n" s="0">
+        <v>603900.0</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>627400.0</v>
+      </c>
+      <c r="P2" t="n" s="0">
+        <v>1285700.0</v>
+      </c>
+      <c r="Q2" t="n" s="0">
+        <v>698000.0</v>
+      </c>
+      <c r="R2" t="n" s="0">
+        <v>571600.0</v>
+      </c>
+      <c r="S2" t="n" s="0">
+        <v>583600.0</v>
+      </c>
+      <c r="T2" t="n" s="0">
         <v>1168300.0</v>
       </c>
-      <c r="L2" t="n" s="0">
-        <v>1130400.0</v>
-      </c>
-      <c r="M2" t="n" s="0">
-        <v>896800.0</v>
-      </c>
-      <c r="N2" t="n" s="0">
-        <v>894100.0</v>
-      </c>
-      <c r="O2" t="n" s="0">
-        <v>1244700.0</v>
-      </c>
-      <c r="P2" t="n" s="0">
-        <v>577100.0</v>
-      </c>
-      <c r="Q2" t="n" s="0">
-        <v>1186400.0</v>
-      </c>
-      <c r="R2" t="n" s="0">
-        <v>577100.0</v>
-      </c>
-      <c r="S2" t="n" s="0">
-        <v>612400.0</v>
-      </c>
-      <c r="T2" t="n" s="0">
-        <v>587100.0</v>
-      </c>
       <c r="U2" t="n" s="0">
-        <v>585500.0</v>
+        <v>1161600.0</v>
       </c>
       <c r="V2" t="n" s="0">
-        <v>1199600.0</v>
+        <v>576000.0</v>
       </c>
       <c r="W2" t="n" s="0">
-        <v>1032990.0</v>
+        <v>868335.0</v>
       </c>
     </row>
     <row r="3">
@@ -293,67 +293,67 @@
         <v>1000.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>1438200.0</v>
+        <v>95000.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>415800.0</v>
+        <v>93900.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1361000.0</v>
+        <v>81200.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>277400.0</v>
+        <v>46700.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>96700.0</v>
+        <v>45300.0</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>84800.0</v>
+        <v>44900.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>94500.0</v>
+        <v>53700.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>46400.0</v>
+        <v>46700.0</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>45100.0</v>
+        <v>44800.0</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>45300.0</v>
+        <v>46300.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>47400.0</v>
+        <v>45600.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>44300.0</v>
+        <v>92300.0</v>
       </c>
       <c r="O3" t="n" s="0">
-        <v>46600.0</v>
+        <v>48000.0</v>
       </c>
       <c r="P3" t="n" s="0">
-        <v>60400.0</v>
+        <v>47300.0</v>
       </c>
       <c r="Q3" t="n" s="0">
+        <v>46500.0</v>
+      </c>
+      <c r="R3" t="n" s="0">
         <v>46200.0</v>
       </c>
-      <c r="R3" t="n" s="0">
-        <v>45000.0</v>
-      </c>
       <c r="S3" t="n" s="0">
-        <v>45800.0</v>
+        <v>47100.0</v>
       </c>
       <c r="T3" t="n" s="0">
         <v>51200.0</v>
       </c>
       <c r="U3" t="n" s="0">
-        <v>46500.0</v>
+        <v>50600.0</v>
       </c>
       <c r="V3" t="n" s="0">
-        <v>46000.0</v>
+        <v>51900.0</v>
       </c>
       <c r="W3" t="n" s="0">
-        <v>219230.0</v>
+        <v>56260.0</v>
       </c>
     </row>
     <row r="4">
@@ -364,67 +364,67 @@
         <v>1000.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>1785500.0</v>
+        <v>269700.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>444300.0</v>
+        <v>224900.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>307000.0</v>
+        <v>295200.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>211900.0</v>
+        <v>212200.0</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>430900.0</v>
+        <v>354000.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>326400.0</v>
+        <v>274100.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>317100.0</v>
+        <v>222300.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>213000.0</v>
+        <v>212500.0</v>
       </c>
       <c r="K4" t="n" s="0">
-        <v>442200.0</v>
+        <v>210700.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>271300.0</v>
+        <v>218800.0</v>
       </c>
       <c r="M4" t="n" s="0">
-        <v>211800.0</v>
+        <v>212600.0</v>
       </c>
       <c r="N4" t="n" s="0">
-        <v>210200.0</v>
+        <v>254400.0</v>
       </c>
       <c r="O4" t="n" s="0">
-        <v>211900.0</v>
+        <v>215900.0</v>
       </c>
       <c r="P4" t="n" s="0">
+        <v>211000.0</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>217700.0</v>
+      </c>
+      <c r="R4" t="n" s="0">
+        <v>456100.0</v>
+      </c>
+      <c r="S4" t="n" s="0">
+        <v>211700.0</v>
+      </c>
+      <c r="T4" t="n" s="0">
         <v>212100.0</v>
       </c>
-      <c r="Q4" t="n" s="0">
-        <v>212900.0</v>
-      </c>
-      <c r="R4" t="n" s="0">
-        <v>211300.0</v>
-      </c>
-      <c r="S4" t="n" s="0">
-        <v>219600.0</v>
-      </c>
-      <c r="T4" t="n" s="0">
-        <v>254000.0</v>
-      </c>
       <c r="U4" t="n" s="0">
-        <v>227100.0</v>
+        <v>211500.0</v>
       </c>
       <c r="V4" t="n" s="0">
-        <v>220600.0</v>
+        <v>241900.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>347055.0</v>
+        <v>246965.0</v>
       </c>
     </row>
     <row r="5">
@@ -435,67 +435,67 @@
         <v>1000.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>427700.0</v>
+        <v>172100.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>102900.0</v>
+        <v>82100.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>189400.0</v>
+        <v>111800.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>95500.0</v>
+        <v>75300.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>93800.0</v>
+        <v>75700.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>106700.0</v>
+        <v>121700.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>114400.0</v>
+        <v>77400.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>72400.0</v>
+        <v>87100.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>79600.0</v>
+        <v>72500.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>102200.0</v>
+        <v>79500.0</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>83100.0</v>
+        <v>74700.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>79400.0</v>
+        <v>93700.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>97800.0</v>
+        <v>72100.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>75700.0</v>
+        <v>144400.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>74300.0</v>
+        <v>75000.0</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>87500.0</v>
+        <v>73200.0</v>
       </c>
       <c r="S5" t="n" s="0">
-        <v>70600.0</v>
+        <v>76100.0</v>
       </c>
       <c r="T5" t="n" s="0">
-        <v>187100.0</v>
+        <v>109900.0</v>
       </c>
       <c r="U5" t="n" s="0">
-        <v>70900.0</v>
+        <v>73000.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>86600.0</v>
+        <v>139300.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>114880.0</v>
+        <v>94330.0</v>
       </c>
     </row>
     <row r="6">
@@ -506,67 +506,67 @@
         <v>1000.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>615100.0</v>
+        <v>125200.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>126900.0</v>
+        <v>185300.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>113700.0</v>
+        <v>177600.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>109300.0</v>
+        <v>116600.0</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>105700.0</v>
+        <v>110900.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>144800.0</v>
+        <v>139900.0</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>147500.0</v>
+        <v>175400.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>131800.0</v>
+        <v>123200.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>245400.0</v>
+        <v>101800.0</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>135000.0</v>
+        <v>99300.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>97500.0</v>
+        <v>122900.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>95500.0</v>
+        <v>119300.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>103800.0</v>
+        <v>93100.0</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>100100.0</v>
+        <v>137600.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>107700.0</v>
+        <v>96100.0</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>122400.0</v>
+        <v>102100.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>93500.0</v>
+        <v>96200.0</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>92900.0</v>
+        <v>130900.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>107000.0</v>
+        <v>97900.0</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>135700.0</v>
+        <v>151200.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>146565.0</v>
+        <v>125125.0</v>
       </c>
     </row>
   </sheetData>

--- a/excel/1000(n)/Random_Dataset.xlsx
+++ b/excel/1000(n)/Random_Dataset.xlsx
@@ -222,67 +222,67 @@
         <v>1000.0</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>1047900.0</v>
+        <v>1060400.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1193000.0</v>
+        <v>810100.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1061600.0</v>
+        <v>1070300.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>850300.0</v>
+        <v>1086900.0</v>
       </c>
       <c r="G2" t="n" s="0">
-        <v>1127100.0</v>
+        <v>1142100.0</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>571200.0</v>
+        <v>1122300.0</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>1171200.0</v>
+        <v>1139600.0</v>
       </c>
       <c r="J2" t="n" s="0">
-        <v>589600.0</v>
+        <v>1146800.0</v>
       </c>
       <c r="K2" t="n" s="0">
-        <v>770700.0</v>
+        <v>777500.0</v>
       </c>
       <c r="L2" t="n" s="0">
-        <v>1141400.0</v>
+        <v>714700.0</v>
       </c>
       <c r="M2" t="n" s="0">
-        <v>566600.0</v>
+        <v>580800.0</v>
       </c>
       <c r="N2" t="n" s="0">
-        <v>603900.0</v>
+        <v>1110800.0</v>
       </c>
       <c r="O2" t="n" s="0">
-        <v>627400.0</v>
+        <v>1162000.0</v>
       </c>
       <c r="P2" t="n" s="0">
-        <v>1285700.0</v>
+        <v>1120700.0</v>
       </c>
       <c r="Q2" t="n" s="0">
-        <v>698000.0</v>
+        <v>587700.0</v>
       </c>
       <c r="R2" t="n" s="0">
-        <v>571600.0</v>
+        <v>1119500.0</v>
       </c>
       <c r="S2" t="n" s="0">
-        <v>583600.0</v>
+        <v>575400.0</v>
       </c>
       <c r="T2" t="n" s="0">
-        <v>1168300.0</v>
+        <v>595900.0</v>
       </c>
       <c r="U2" t="n" s="0">
-        <v>1161600.0</v>
+        <v>873900.0</v>
       </c>
       <c r="V2" t="n" s="0">
-        <v>576000.0</v>
+        <v>1122800.0</v>
       </c>
       <c r="W2" t="n" s="0">
-        <v>868335.0</v>
+        <v>946010.0</v>
       </c>
     </row>
     <row r="3">
@@ -293,67 +293,67 @@
         <v>1000.0</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>95000.0</v>
+        <v>94300.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>93900.0</v>
+        <v>96300.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>81200.0</v>
+        <v>98800.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>46700.0</v>
+        <v>94000.0</v>
       </c>
       <c r="G3" t="n" s="0">
-        <v>45300.0</v>
+        <v>91900.0</v>
       </c>
       <c r="H3" t="n" s="0">
-        <v>44900.0</v>
+        <v>91000.0</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>53700.0</v>
+        <v>55100.0</v>
       </c>
       <c r="J3" t="n" s="0">
-        <v>46700.0</v>
+        <v>47700.0</v>
       </c>
       <c r="K3" t="n" s="0">
-        <v>44800.0</v>
+        <v>83300.0</v>
       </c>
       <c r="L3" t="n" s="0">
-        <v>46300.0</v>
+        <v>47700.0</v>
       </c>
       <c r="M3" t="n" s="0">
-        <v>45600.0</v>
+        <v>45700.0</v>
       </c>
       <c r="N3" t="n" s="0">
-        <v>92300.0</v>
+        <v>44100.0</v>
       </c>
       <c r="O3" t="n" s="0">
-        <v>48000.0</v>
+        <v>48400.0</v>
       </c>
       <c r="P3" t="n" s="0">
-        <v>47300.0</v>
+        <v>45900.0</v>
       </c>
       <c r="Q3" t="n" s="0">
-        <v>46500.0</v>
+        <v>46100.0</v>
       </c>
       <c r="R3" t="n" s="0">
-        <v>46200.0</v>
+        <v>45200.0</v>
       </c>
       <c r="S3" t="n" s="0">
-        <v>47100.0</v>
+        <v>46900.0</v>
       </c>
       <c r="T3" t="n" s="0">
-        <v>51200.0</v>
+        <v>101000.0</v>
       </c>
       <c r="U3" t="n" s="0">
-        <v>50600.0</v>
+        <v>46400.0</v>
       </c>
       <c r="V3" t="n" s="0">
-        <v>51900.0</v>
+        <v>100000.0</v>
       </c>
       <c r="W3" t="n" s="0">
-        <v>56260.0</v>
+        <v>68490.0</v>
       </c>
     </row>
     <row r="4">
@@ -364,67 +364,67 @@
         <v>1000.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>269700.0</v>
+        <v>452400.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>224900.0</v>
+        <v>450700.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>295200.0</v>
+        <v>455300.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>212200.0</v>
+        <v>441500.0</v>
       </c>
       <c r="G4" t="n" s="0">
-        <v>354000.0</v>
+        <v>269500.0</v>
       </c>
       <c r="H4" t="n" s="0">
-        <v>274100.0</v>
+        <v>441600.0</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>222300.0</v>
+        <v>212500.0</v>
       </c>
       <c r="J4" t="n" s="0">
-        <v>212500.0</v>
+        <v>229400.0</v>
       </c>
       <c r="K4" t="n" s="0">
+        <v>330500.0</v>
+      </c>
+      <c r="L4" t="n" s="0">
+        <v>211800.0</v>
+      </c>
+      <c r="M4" t="n" s="0">
+        <v>212700.0</v>
+      </c>
+      <c r="N4" t="n" s="0">
+        <v>217100.0</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>211900.0</v>
+      </c>
+      <c r="P4" t="n" s="0">
+        <v>211600.0</v>
+      </c>
+      <c r="Q4" t="n" s="0">
+        <v>213700.0</v>
+      </c>
+      <c r="R4" t="n" s="0">
+        <v>214800.0</v>
+      </c>
+      <c r="S4" t="n" s="0">
+        <v>211600.0</v>
+      </c>
+      <c r="T4" t="n" s="0">
+        <v>441900.0</v>
+      </c>
+      <c r="U4" t="n" s="0">
         <v>210700.0</v>
       </c>
-      <c r="L4" t="n" s="0">
-        <v>218800.0</v>
-      </c>
-      <c r="M4" t="n" s="0">
-        <v>212600.0</v>
-      </c>
-      <c r="N4" t="n" s="0">
-        <v>254400.0</v>
-      </c>
-      <c r="O4" t="n" s="0">
-        <v>215900.0</v>
-      </c>
-      <c r="P4" t="n" s="0">
-        <v>211000.0</v>
-      </c>
-      <c r="Q4" t="n" s="0">
-        <v>217700.0</v>
-      </c>
-      <c r="R4" t="n" s="0">
-        <v>456100.0</v>
-      </c>
-      <c r="S4" t="n" s="0">
-        <v>211700.0</v>
-      </c>
-      <c r="T4" t="n" s="0">
-        <v>212100.0</v>
-      </c>
-      <c r="U4" t="n" s="0">
-        <v>211500.0</v>
-      </c>
       <c r="V4" t="n" s="0">
-        <v>241900.0</v>
+        <v>445900.0</v>
       </c>
       <c r="W4" t="n" s="0">
-        <v>246965.0</v>
+        <v>304355.0</v>
       </c>
     </row>
     <row r="5">
@@ -435,67 +435,67 @@
         <v>1000.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>172100.0</v>
+        <v>143300.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>82100.0</v>
+        <v>162000.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>111800.0</v>
+        <v>297600.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>75300.0</v>
+        <v>104800.0</v>
       </c>
       <c r="G5" t="n" s="0">
-        <v>75700.0</v>
+        <v>70600.0</v>
       </c>
       <c r="H5" t="n" s="0">
-        <v>121700.0</v>
+        <v>130900.0</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>77400.0</v>
+        <v>102000.0</v>
       </c>
       <c r="J5" t="n" s="0">
-        <v>87100.0</v>
+        <v>75500.0</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>72500.0</v>
+        <v>105400.0</v>
       </c>
       <c r="L5" t="n" s="0">
-        <v>79500.0</v>
+        <v>87200.0</v>
       </c>
       <c r="M5" t="n" s="0">
-        <v>74700.0</v>
+        <v>137400.0</v>
       </c>
       <c r="N5" t="n" s="0">
-        <v>93700.0</v>
+        <v>91500.0</v>
       </c>
       <c r="O5" t="n" s="0">
-        <v>72100.0</v>
+        <v>73100.0</v>
       </c>
       <c r="P5" t="n" s="0">
-        <v>144400.0</v>
+        <v>73200.0</v>
       </c>
       <c r="Q5" t="n" s="0">
-        <v>75000.0</v>
+        <v>78600.0</v>
       </c>
       <c r="R5" t="n" s="0">
-        <v>73200.0</v>
+        <v>75500.0</v>
       </c>
       <c r="S5" t="n" s="0">
-        <v>76100.0</v>
+        <v>73000.0</v>
       </c>
       <c r="T5" t="n" s="0">
-        <v>109900.0</v>
+        <v>76200.0</v>
       </c>
       <c r="U5" t="n" s="0">
-        <v>73000.0</v>
+        <v>71400.0</v>
       </c>
       <c r="V5" t="n" s="0">
-        <v>139300.0</v>
+        <v>125600.0</v>
       </c>
       <c r="W5" t="n" s="0">
-        <v>94330.0</v>
+        <v>107740.0</v>
       </c>
     </row>
     <row r="6">
@@ -506,67 +506,67 @@
         <v>1000.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>125200.0</v>
+        <v>172000.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>185300.0</v>
+        <v>148300.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>177600.0</v>
+        <v>158900.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>116600.0</v>
+        <v>150500.0</v>
       </c>
       <c r="G6" t="n" s="0">
-        <v>110900.0</v>
+        <v>269600.0</v>
       </c>
       <c r="H6" t="n" s="0">
-        <v>139900.0</v>
+        <v>119900.0</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>175400.0</v>
+        <v>150100.0</v>
       </c>
       <c r="J6" t="n" s="0">
-        <v>123200.0</v>
+        <v>98200.0</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>101800.0</v>
+        <v>104400.0</v>
       </c>
       <c r="L6" t="n" s="0">
-        <v>99300.0</v>
+        <v>105200.0</v>
       </c>
       <c r="M6" t="n" s="0">
-        <v>122900.0</v>
+        <v>153300.0</v>
       </c>
       <c r="N6" t="n" s="0">
-        <v>119300.0</v>
+        <v>157700.0</v>
       </c>
       <c r="O6" t="n" s="0">
-        <v>93100.0</v>
+        <v>96000.0</v>
       </c>
       <c r="P6" t="n" s="0">
-        <v>137600.0</v>
+        <v>97300.0</v>
       </c>
       <c r="Q6" t="n" s="0">
-        <v>96100.0</v>
+        <v>96800.0</v>
       </c>
       <c r="R6" t="n" s="0">
-        <v>102100.0</v>
+        <v>96600.0</v>
       </c>
       <c r="S6" t="n" s="0">
-        <v>96200.0</v>
+        <v>95500.0</v>
       </c>
       <c r="T6" t="n" s="0">
-        <v>130900.0</v>
+        <v>100900.0</v>
       </c>
       <c r="U6" t="n" s="0">
-        <v>97900.0</v>
+        <v>103500.0</v>
       </c>
       <c r="V6" t="n" s="0">
-        <v>151200.0</v>
+        <v>149500.0</v>
       </c>
       <c r="W6" t="n" s="0">
-        <v>125125.0</v>
+        <v>131210.0</v>
       </c>
     </row>
   </sheetData>
